--- a/test-import-mixed.xlsx
+++ b/test-import-mixed.xlsx
@@ -799,10 +799,10 @@
         <v>39</v>
       </c>
       <c r="F2" s="2">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
@@ -831,10 +831,10 @@
         <v>39</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>1</v>
